--- a/datasets/Roosevelt/MatchupTable.xlsx
+++ b/datasets/Roosevelt/MatchupTable.xlsx
@@ -546,10 +546,8 @@
           <t>179.15</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C3" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
@@ -566,8 +564,10 @@
           <t>thru</t>
         </is>
       </c>
-      <c r="G3" s="1" t="n">
-        <v/>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>2231157628</t>
+        </is>
       </c>
       <c r="H3" s="1" t="n">
         <v/>
@@ -583,8 +583,10 @@
           <t>Synchro_signal.csv</t>
         </is>
       </c>
-      <c r="L3" s="1" t="n">
-        <v/>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>2231157628</t>
+        </is>
       </c>
       <c r="M3" s="1" t="n">
         <v/>
@@ -602,10 +604,8 @@
           <t>179.15</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C4" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -642,10 +642,8 @@
           <t>269.58</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C5" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
@@ -682,10 +680,8 @@
           <t>359.09</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C6" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
@@ -722,10 +718,8 @@
           <t>359.09</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C7" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -766,10 +760,8 @@
           <t>179.58</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C8" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
@@ -786,8 +778,10 @@
           <t>thru</t>
         </is>
       </c>
-      <c r="G8" s="1" t="n">
-        <v/>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>4334657982</t>
+        </is>
       </c>
       <c r="H8" s="1" t="n">
         <v/>
@@ -799,8 +793,10 @@
         <v/>
       </c>
       <c r="K8" s="1" t="n"/>
-      <c r="L8" s="1" t="n">
-        <v/>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>4334657982</t>
+        </is>
       </c>
       <c r="M8" s="1" t="n">
         <v/>
@@ -818,10 +814,8 @@
           <t>358.14</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C9" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
@@ -859,13 +853,11 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>89.74</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>89.58</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -882,8 +874,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G10" s="1" t="n">
-        <v/>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>5638144537</t>
+        </is>
       </c>
       <c r="H10" s="1" t="n">
         <v/>
@@ -895,8 +889,10 @@
         <v/>
       </c>
       <c r="K10" s="1" t="n"/>
-      <c r="L10" s="1" t="n">
-        <v/>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>5638144537</t>
+        </is>
       </c>
       <c r="M10" s="1" t="n">
         <v/>
@@ -911,13 +907,11 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>89.74</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>89.58</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -955,13 +949,11 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>157.69</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>157.5</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -978,8 +970,10 @@
           <t>thru</t>
         </is>
       </c>
-      <c r="G12" s="1" t="n">
-        <v/>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>5913700349</t>
+        </is>
       </c>
       <c r="H12" s="1" t="n">
         <v/>
@@ -991,8 +985,10 @@
         <v/>
       </c>
       <c r="K12" s="1" t="n"/>
-      <c r="L12" s="1" t="n">
-        <v/>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>5913700349</t>
+        </is>
       </c>
       <c r="M12" s="1" t="n">
         <v/>
@@ -1010,10 +1006,8 @@
           <t>359.32</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C13" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
@@ -1051,13 +1045,11 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>269.23</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>269.34</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
@@ -1074,8 +1066,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G14" s="1" t="n">
-        <v/>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>cluster10088633497_2565193676</t>
+        </is>
       </c>
       <c r="H14" s="1" t="n">
         <v/>
@@ -1087,8 +1081,10 @@
         <v/>
       </c>
       <c r="K14" s="1" t="n"/>
-      <c r="L14" s="1" t="n">
-        <v/>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>cluster10088633497_2565193676</t>
+        </is>
       </c>
       <c r="M14" s="1" t="n">
         <v/>
@@ -1106,10 +1102,8 @@
           <t>358.4</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C15" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
@@ -1146,10 +1140,8 @@
           <t>358.4</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C16" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -1190,10 +1182,8 @@
           <t>88.86</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C17" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
@@ -1210,8 +1200,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G17" s="1" t="n">
-        <v/>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>cluster10112297888_cluster_2231157610_2231157618</t>
+        </is>
       </c>
       <c r="H17" s="1" t="n">
         <v/>
@@ -1223,8 +1215,10 @@
         <v/>
       </c>
       <c r="K17" s="1" t="n"/>
-      <c r="L17" s="1" t="n">
-        <v/>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>cluster10112297888_cluster_2231157610_2231157618</t>
+        </is>
       </c>
       <c r="M17" s="1" t="n">
         <v/>
@@ -1242,10 +1236,8 @@
           <t>88.86</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C18" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
@@ -1282,10 +1274,8 @@
           <t>179.2</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C19" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
@@ -1322,10 +1312,8 @@
           <t>179.2</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C20" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -1362,10 +1350,8 @@
           <t>357.88</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C21" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
@@ -1402,10 +1388,8 @@
           <t>357.88</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C22" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
@@ -1443,13 +1427,11 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>89.06</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>89.09</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
@@ -1466,8 +1448,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G23" s="1" t="n">
-        <v/>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>cluster10842139397_10842139398</t>
+        </is>
       </c>
       <c r="H23" s="1" t="n">
         <v/>
@@ -1479,8 +1463,10 @@
         <v/>
       </c>
       <c r="K23" s="1" t="n"/>
-      <c r="L23" s="1" t="n">
-        <v/>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>cluster10842139397_10842139398</t>
+        </is>
       </c>
       <c r="M23" s="1" t="n">
         <v/>
@@ -1495,13 +1481,11 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>89.06</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>89.09</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
@@ -1535,13 +1519,11 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>178.48</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>178.37</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
@@ -1575,13 +1557,11 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>178.48</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>178.37</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1618,10 +1598,8 @@
           <t>359.75</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C27" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1658,10 +1636,8 @@
           <t>359.75</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C28" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
@@ -1702,10 +1678,8 @@
           <t>179.25</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C29" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1722,8 +1696,10 @@
           <t>thru</t>
         </is>
       </c>
-      <c r="G29" s="1" t="n">
-        <v/>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>cluster12070882025_cluster_12074267602_2231157639</t>
+        </is>
       </c>
       <c r="H29" s="1" t="n">
         <v/>
@@ -1735,8 +1711,10 @@
         <v/>
       </c>
       <c r="K29" s="1" t="n"/>
-      <c r="L29" s="1" t="n">
-        <v/>
+      <c r="L29" s="1" t="inlineStr">
+        <is>
+          <t>cluster12070882025_cluster_12074267602_2231157639</t>
+        </is>
       </c>
       <c r="M29" s="1" t="n">
         <v/>
@@ -1754,10 +1732,8 @@
           <t>179.25</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C30" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1794,10 +1770,8 @@
           <t>268.69</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C31" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -1834,10 +1808,8 @@
           <t>268.69</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C32" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
@@ -1874,10 +1846,8 @@
           <t>359.45</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C33" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
@@ -1914,10 +1884,8 @@
           <t>359.45</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C34" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1955,13 +1923,11 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>177.2</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>177.44</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
@@ -1978,8 +1944,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G35" s="1" t="n">
-        <v/>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>cluster2207479881_5913357343_704695657</t>
+        </is>
       </c>
       <c r="H35" s="1" t="n">
         <v/>
@@ -1991,8 +1959,10 @@
         <v/>
       </c>
       <c r="K35" s="1" t="n"/>
-      <c r="L35" s="1" t="n">
-        <v/>
+      <c r="L35" s="1" t="inlineStr">
+        <is>
+          <t>cluster2207479881_5913357343_704695657</t>
+        </is>
       </c>
       <c r="M35" s="1" t="n">
         <v/>
@@ -2007,13 +1977,11 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>269.01</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>269.09</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -2047,13 +2015,11 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>269.01</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>269.09</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
@@ -2091,13 +2057,11 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>180.7</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>180.67</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
@@ -2114,8 +2078,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G38" s="1" t="n">
-        <v/>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>cluster3813046358_8117713224</t>
+        </is>
       </c>
       <c r="H38" s="1" t="n">
         <v/>
@@ -2127,8 +2093,10 @@
         <v/>
       </c>
       <c r="K38" s="1" t="n"/>
-      <c r="L38" s="1" t="n">
-        <v/>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t>cluster3813046358_8117713224</t>
+        </is>
       </c>
       <c r="M38" s="1" t="n">
         <v/>
@@ -2143,13 +2111,11 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>269.33</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>269.34</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
@@ -2183,13 +2149,11 @@
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>269.33</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>269.34</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
@@ -2230,10 +2194,8 @@
           <t>89.12</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C41" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
@@ -2250,8 +2212,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G41" s="1" t="n">
-        <v/>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>cluster5913357342_704695655_704695706</t>
+        </is>
       </c>
       <c r="H41" s="1" t="n">
         <v/>
@@ -2263,8 +2227,10 @@
         <v/>
       </c>
       <c r="K41" s="1" t="n"/>
-      <c r="L41" s="1" t="n">
-        <v/>
+      <c r="L41" s="1" t="inlineStr">
+        <is>
+          <t>cluster5913357342_704695655_704695706</t>
+        </is>
       </c>
       <c r="M41" s="1" t="n">
         <v/>
@@ -2282,10 +2248,8 @@
           <t>89.12</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C42" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
@@ -2322,10 +2286,8 @@
           <t>269.57</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C43" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
@@ -2362,10 +2324,8 @@
           <t>269.57</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C44" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
@@ -2402,10 +2362,8 @@
           <t>353.49</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="C45" s="1" t="n">
+        <v>35</v>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
@@ -2442,10 +2400,8 @@
           <t>353.49</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="C46" s="1" t="n">
+        <v>35</v>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
@@ -2486,10 +2442,8 @@
           <t>89.57</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C47" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
@@ -2506,8 +2460,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G47" s="1" t="n">
-        <v/>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>cluster5913700334_5913700336</t>
+        </is>
       </c>
       <c r="H47" s="1" t="n">
         <v/>
@@ -2519,8 +2475,10 @@
         <v/>
       </c>
       <c r="K47" s="1" t="n"/>
-      <c r="L47" s="1" t="n">
-        <v/>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t>cluster5913700334_5913700336</t>
+        </is>
       </c>
       <c r="M47" s="1" t="n">
         <v/>
@@ -2538,10 +2496,8 @@
           <t>89.57</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C48" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -2582,10 +2538,8 @@
           <t>89.45</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C49" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
@@ -2602,32 +2556,40 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G49" s="1" t="n">
-        <v/>
-      </c>
-      <c r="H49" s="1" t="n">
-        <v/>
-      </c>
-      <c r="I49" s="1" t="n">
-        <v/>
-      </c>
-      <c r="J49" s="1" t="n">
-        <v/>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>cluster_1105879188_1105879277_1105879560_1105879625_#8more</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>03112025</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>Roosevelt and Clark</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>EBR</t>
+        </is>
       </c>
       <c r="K49" s="1" t="n"/>
       <c r="L49" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>cluster_1105879188_1105879277_1105879560_1105879625_#8more</t>
         </is>
       </c>
       <c r="M49" s="1" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>EBR</t>
         </is>
       </c>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2600,8 @@
           <t>89.45</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C50" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
@@ -2661,14 +2621,16 @@
       <c r="G50" s="1" t="n"/>
       <c r="H50" s="1" t="n"/>
       <c r="I50" s="1" t="n"/>
-      <c r="J50" s="1" t="n">
-        <v/>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>EBT</t>
+        </is>
       </c>
       <c r="K50" s="1" t="n"/>
       <c r="L50" s="1" t="n"/>
       <c r="M50" s="1" t="inlineStr">
         <is>
-          <t>NBT</t>
+          <t>EBT</t>
         </is>
       </c>
       <c r="N50" s="1" t="n"/>
@@ -2680,10 +2642,8 @@
           <t>89.45</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C51" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
@@ -2703,14 +2663,16 @@
       <c r="G51" s="1" t="n"/>
       <c r="H51" s="1" t="n"/>
       <c r="I51" s="1" t="n"/>
-      <c r="J51" s="1" t="n">
-        <v/>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>EBL</t>
+        </is>
       </c>
       <c r="K51" s="1" t="n"/>
       <c r="L51" s="1" t="n"/>
       <c r="M51" s="1" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="N51" s="1" t="n"/>
@@ -2722,10 +2684,8 @@
           <t>89.45</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C52" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
@@ -2745,14 +2705,16 @@
       <c r="G52" s="1" t="n"/>
       <c r="H52" s="1" t="n"/>
       <c r="I52" s="1" t="n"/>
-      <c r="J52" s="1" t="n">
-        <v/>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>EBU</t>
+        </is>
       </c>
       <c r="K52" s="1" t="n"/>
       <c r="L52" s="1" t="n"/>
       <c r="M52" s="1" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>EBU</t>
         </is>
       </c>
       <c r="N52" s="1" t="n"/>
@@ -2764,10 +2726,8 @@
           <t>175.61</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C53" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
@@ -2787,14 +2747,16 @@
       <c r="G53" s="1" t="n"/>
       <c r="H53" s="1" t="n"/>
       <c r="I53" s="1" t="n"/>
-      <c r="J53" s="1" t="n">
-        <v/>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>SBR</t>
+        </is>
       </c>
       <c r="K53" s="1" t="n"/>
       <c r="L53" s="1" t="n"/>
       <c r="M53" s="1" t="inlineStr">
         <is>
-          <t>EBR</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="N53" s="1" t="n"/>
@@ -2806,10 +2768,8 @@
           <t>175.61</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C54" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
@@ -2829,14 +2789,16 @@
       <c r="G54" s="1" t="n"/>
       <c r="H54" s="1" t="n"/>
       <c r="I54" s="1" t="n"/>
-      <c r="J54" s="1" t="n">
-        <v/>
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>SBT</t>
+        </is>
       </c>
       <c r="K54" s="1" t="n"/>
       <c r="L54" s="1" t="n"/>
       <c r="M54" s="1" t="inlineStr">
         <is>
-          <t>EBT</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="N54" s="1" t="n"/>
@@ -2848,10 +2810,8 @@
           <t>175.61</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C55" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
@@ -2871,14 +2831,16 @@
       <c r="G55" s="1" t="n"/>
       <c r="H55" s="1" t="n"/>
       <c r="I55" s="1" t="n"/>
-      <c r="J55" s="1" t="n">
-        <v/>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>SBL</t>
+        </is>
       </c>
       <c r="K55" s="1" t="n"/>
       <c r="L55" s="1" t="n"/>
       <c r="M55" s="1" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="N55" s="1" t="n"/>
@@ -2890,10 +2852,8 @@
           <t>175.61</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C56" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
@@ -2913,14 +2873,16 @@
       <c r="G56" s="1" t="n"/>
       <c r="H56" s="1" t="n"/>
       <c r="I56" s="1" t="n"/>
-      <c r="J56" s="1" t="n">
-        <v/>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>SBU</t>
+        </is>
       </c>
       <c r="K56" s="1" t="n"/>
       <c r="L56" s="1" t="n"/>
       <c r="M56" s="1" t="inlineStr">
         <is>
-          <t>EBU</t>
+          <t>SBU</t>
         </is>
       </c>
       <c r="N56" s="1" t="n"/>
@@ -2932,10 +2894,8 @@
           <t>268.98</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C57" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
@@ -2955,14 +2915,16 @@
       <c r="G57" s="1" t="n"/>
       <c r="H57" s="1" t="n"/>
       <c r="I57" s="1" t="n"/>
-      <c r="J57" s="1" t="n">
-        <v/>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>WBR</t>
+        </is>
       </c>
       <c r="K57" s="1" t="n"/>
       <c r="L57" s="1" t="n"/>
       <c r="M57" s="1" t="inlineStr">
         <is>
-          <t>SBR</t>
+          <t>WBR</t>
         </is>
       </c>
       <c r="N57" s="1" t="n"/>
@@ -2974,10 +2936,8 @@
           <t>268.98</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C58" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
@@ -2997,14 +2957,16 @@
       <c r="G58" s="1" t="n"/>
       <c r="H58" s="1" t="n"/>
       <c r="I58" s="1" t="n"/>
-      <c r="J58" s="1" t="n">
-        <v/>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
       </c>
       <c r="K58" s="1" t="n"/>
       <c r="L58" s="1" t="n"/>
       <c r="M58" s="1" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="N58" s="1" t="n"/>
@@ -3016,10 +2978,8 @@
           <t>268.98</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C59" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
@@ -3039,14 +2999,16 @@
       <c r="G59" s="1" t="n"/>
       <c r="H59" s="1" t="n"/>
       <c r="I59" s="1" t="n"/>
-      <c r="J59" s="1" t="n">
-        <v/>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>WBL</t>
+        </is>
       </c>
       <c r="K59" s="1" t="n"/>
       <c r="L59" s="1" t="n"/>
       <c r="M59" s="1" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>WBL</t>
         </is>
       </c>
       <c r="N59" s="1" t="n"/>
@@ -3058,10 +3020,8 @@
           <t>268.98</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C60" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
@@ -3081,14 +3041,16 @@
       <c r="G60" s="1" t="n"/>
       <c r="H60" s="1" t="n"/>
       <c r="I60" s="1" t="n"/>
-      <c r="J60" s="1" t="n">
-        <v/>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>WBU</t>
+        </is>
       </c>
       <c r="K60" s="1" t="n"/>
       <c r="L60" s="1" t="n"/>
       <c r="M60" s="1" t="inlineStr">
         <is>
-          <t>SBU</t>
+          <t>WBU</t>
         </is>
       </c>
       <c r="N60" s="1" t="n"/>
@@ -3100,10 +3062,8 @@
           <t>357.03</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C61" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
@@ -3123,14 +3083,16 @@
       <c r="G61" s="1" t="n"/>
       <c r="H61" s="1" t="n"/>
       <c r="I61" s="1" t="n"/>
-      <c r="J61" s="1" t="n">
-        <v/>
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t>NBR</t>
+        </is>
       </c>
       <c r="K61" s="1" t="n"/>
       <c r="L61" s="1" t="n"/>
       <c r="M61" s="1" t="inlineStr">
         <is>
-          <t>WBR</t>
+          <t>NBR</t>
         </is>
       </c>
       <c r="N61" s="1" t="n"/>
@@ -3142,10 +3104,8 @@
           <t>357.03</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C62" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
@@ -3165,14 +3125,16 @@
       <c r="G62" s="1" t="n"/>
       <c r="H62" s="1" t="n"/>
       <c r="I62" s="1" t="n"/>
-      <c r="J62" s="1" t="n">
-        <v/>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>NBT</t>
+        </is>
       </c>
       <c r="K62" s="1" t="n"/>
       <c r="L62" s="1" t="n"/>
       <c r="M62" s="1" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>NBT</t>
         </is>
       </c>
       <c r="N62" s="1" t="n"/>
@@ -3184,10 +3146,8 @@
           <t>357.03</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C63" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
@@ -3207,14 +3167,16 @@
       <c r="G63" s="1" t="n"/>
       <c r="H63" s="1" t="n"/>
       <c r="I63" s="1" t="n"/>
-      <c r="J63" s="1" t="n">
-        <v/>
+      <c r="J63" s="1" t="inlineStr">
+        <is>
+          <t>NBL</t>
+        </is>
       </c>
       <c r="K63" s="1" t="n"/>
       <c r="L63" s="1" t="n"/>
       <c r="M63" s="1" t="inlineStr">
         <is>
-          <t>WBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="N63" s="1" t="n"/>
@@ -3226,10 +3188,8 @@
           <t>357.03</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C64" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
@@ -3249,14 +3209,16 @@
       <c r="G64" s="1" t="n"/>
       <c r="H64" s="1" t="n"/>
       <c r="I64" s="1" t="n"/>
-      <c r="J64" s="1" t="n">
-        <v/>
+      <c r="J64" s="1" t="inlineStr">
+        <is>
+          <t>NBU</t>
+        </is>
       </c>
       <c r="K64" s="1" t="n"/>
       <c r="L64" s="1" t="n"/>
       <c r="M64" s="1" t="inlineStr">
         <is>
-          <t>WBU</t>
+          <t>NBU</t>
         </is>
       </c>
       <c r="N64" s="1" t="n"/>
@@ -3272,10 +3234,8 @@
           <t>178.36</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C65" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
@@ -3292,8 +3252,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G65" s="1" t="n">
-        <v/>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>cluster_12070882012_12070882220_12070882269_1961538051</t>
+        </is>
       </c>
       <c r="H65" s="1" t="n">
         <v/>
@@ -3305,8 +3267,10 @@
         <v/>
       </c>
       <c r="K65" s="1" t="n"/>
-      <c r="L65" s="1" t="n">
-        <v/>
+      <c r="L65" s="1" t="inlineStr">
+        <is>
+          <t>cluster_12070882012_12070882220_12070882269_1961538051</t>
+        </is>
       </c>
       <c r="M65" s="1" t="n">
         <v/>
@@ -3324,10 +3288,8 @@
           <t>268.3</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C66" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
@@ -3364,10 +3326,8 @@
           <t>268.3</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C67" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
@@ -3408,10 +3368,8 @@
           <t>89.84</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C68" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
@@ -3428,32 +3386,40 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G68" s="1" t="n">
-        <v/>
-      </c>
-      <c r="H68" s="1" t="n">
-        <v/>
-      </c>
-      <c r="I68" s="1" t="n">
-        <v/>
-      </c>
-      <c r="J68" s="1" t="n">
-        <v/>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>cluster_1655457006_1655457009_5906917264_5913542432_#4more</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="inlineStr">
+        <is>
+          <t>03112025</t>
+        </is>
+      </c>
+      <c r="I68" s="1" t="inlineStr">
+        <is>
+          <t>Canal-Roosevelt</t>
+        </is>
+      </c>
+      <c r="J68" s="1" t="inlineStr">
+        <is>
+          <t>EBR</t>
+        </is>
       </c>
       <c r="K68" s="1" t="n"/>
       <c r="L68" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>cluster_1655457006_1655457009_5906917264_5913542432_#4more</t>
         </is>
       </c>
       <c r="M68" s="1" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>EBR</t>
         </is>
       </c>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -3464,10 +3430,8 @@
           <t>89.84</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C69" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
@@ -3487,14 +3451,16 @@
       <c r="G69" s="1" t="n"/>
       <c r="H69" s="1" t="n"/>
       <c r="I69" s="1" t="n"/>
-      <c r="J69" s="1" t="n">
-        <v/>
+      <c r="J69" s="1" t="inlineStr">
+        <is>
+          <t>EBT</t>
+        </is>
       </c>
       <c r="K69" s="1" t="n"/>
       <c r="L69" s="1" t="n"/>
       <c r="M69" s="1" t="inlineStr">
         <is>
-          <t>NBT</t>
+          <t>EBT</t>
         </is>
       </c>
       <c r="N69" s="1" t="n"/>
@@ -3506,10 +3472,8 @@
           <t>89.84</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C70" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
@@ -3529,14 +3493,16 @@
       <c r="G70" s="1" t="n"/>
       <c r="H70" s="1" t="n"/>
       <c r="I70" s="1" t="n"/>
-      <c r="J70" s="1" t="n">
-        <v/>
+      <c r="J70" s="1" t="inlineStr">
+        <is>
+          <t>EBL</t>
+        </is>
       </c>
       <c r="K70" s="1" t="n"/>
       <c r="L70" s="1" t="n"/>
       <c r="M70" s="1" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="N70" s="1" t="n"/>
@@ -3548,10 +3514,8 @@
           <t>89.84</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C71" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
@@ -3571,14 +3535,16 @@
       <c r="G71" s="1" t="n"/>
       <c r="H71" s="1" t="n"/>
       <c r="I71" s="1" t="n"/>
-      <c r="J71" s="1" t="n">
-        <v/>
+      <c r="J71" s="1" t="inlineStr">
+        <is>
+          <t>EBU</t>
+        </is>
       </c>
       <c r="K71" s="1" t="n"/>
       <c r="L71" s="1" t="n"/>
       <c r="M71" s="1" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>EBU</t>
         </is>
       </c>
       <c r="N71" s="1" t="n"/>
@@ -3587,13 +3553,11 @@
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>178.39</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>178.41</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
@@ -3613,14 +3577,16 @@
       <c r="G72" s="1" t="n"/>
       <c r="H72" s="1" t="n"/>
       <c r="I72" s="1" t="n"/>
-      <c r="J72" s="1" t="n">
-        <v/>
+      <c r="J72" s="1" t="inlineStr">
+        <is>
+          <t>SBR</t>
+        </is>
       </c>
       <c r="K72" s="1" t="n"/>
       <c r="L72" s="1" t="n"/>
       <c r="M72" s="1" t="inlineStr">
         <is>
-          <t>EBR</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="N72" s="1" t="n"/>
@@ -3629,13 +3595,11 @@
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>178.39</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>178.41</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
@@ -3655,14 +3619,16 @@
       <c r="G73" s="1" t="n"/>
       <c r="H73" s="1" t="n"/>
       <c r="I73" s="1" t="n"/>
-      <c r="J73" s="1" t="n">
-        <v/>
+      <c r="J73" s="1" t="inlineStr">
+        <is>
+          <t>SBT</t>
+        </is>
       </c>
       <c r="K73" s="1" t="n"/>
       <c r="L73" s="1" t="n"/>
       <c r="M73" s="1" t="inlineStr">
         <is>
-          <t>EBT</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="N73" s="1" t="n"/>
@@ -3671,13 +3637,11 @@
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>178.39</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>178.41</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
@@ -3697,14 +3661,16 @@
       <c r="G74" s="1" t="n"/>
       <c r="H74" s="1" t="n"/>
       <c r="I74" s="1" t="n"/>
-      <c r="J74" s="1" t="n">
-        <v/>
+      <c r="J74" s="1" t="inlineStr">
+        <is>
+          <t>SBL</t>
+        </is>
       </c>
       <c r="K74" s="1" t="n"/>
       <c r="L74" s="1" t="n"/>
       <c r="M74" s="1" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="N74" s="1" t="n"/>
@@ -3713,13 +3679,11 @@
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>178.39</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>178.41</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
@@ -3739,14 +3703,16 @@
       <c r="G75" s="1" t="n"/>
       <c r="H75" s="1" t="n"/>
       <c r="I75" s="1" t="n"/>
-      <c r="J75" s="1" t="n">
-        <v/>
+      <c r="J75" s="1" t="inlineStr">
+        <is>
+          <t>SBU</t>
+        </is>
       </c>
       <c r="K75" s="1" t="n"/>
       <c r="L75" s="1" t="n"/>
       <c r="M75" s="1" t="inlineStr">
         <is>
-          <t>EBU</t>
+          <t>SBU</t>
         </is>
       </c>
       <c r="N75" s="1" t="n"/>
@@ -3755,13 +3721,11 @@
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>269.31</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>269.24</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
@@ -3781,14 +3745,16 @@
       <c r="G76" s="1" t="n"/>
       <c r="H76" s="1" t="n"/>
       <c r="I76" s="1" t="n"/>
-      <c r="J76" s="1" t="n">
-        <v/>
+      <c r="J76" s="1" t="inlineStr">
+        <is>
+          <t>WBR</t>
+        </is>
       </c>
       <c r="K76" s="1" t="n"/>
       <c r="L76" s="1" t="n"/>
       <c r="M76" s="1" t="inlineStr">
         <is>
-          <t>SBR</t>
+          <t>WBR</t>
         </is>
       </c>
       <c r="N76" s="1" t="n"/>
@@ -3797,13 +3763,11 @@
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>269.31</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>269.24</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
@@ -3823,14 +3787,16 @@
       <c r="G77" s="1" t="n"/>
       <c r="H77" s="1" t="n"/>
       <c r="I77" s="1" t="n"/>
-      <c r="J77" s="1" t="n">
-        <v/>
+      <c r="J77" s="1" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
       </c>
       <c r="K77" s="1" t="n"/>
       <c r="L77" s="1" t="n"/>
       <c r="M77" s="1" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="N77" s="1" t="n"/>
@@ -3839,13 +3805,11 @@
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>269.31</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>269.24</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
@@ -3865,14 +3829,16 @@
       <c r="G78" s="1" t="n"/>
       <c r="H78" s="1" t="n"/>
       <c r="I78" s="1" t="n"/>
-      <c r="J78" s="1" t="n">
-        <v/>
+      <c r="J78" s="1" t="inlineStr">
+        <is>
+          <t>WBL</t>
+        </is>
       </c>
       <c r="K78" s="1" t="n"/>
       <c r="L78" s="1" t="n"/>
       <c r="M78" s="1" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>WBL</t>
         </is>
       </c>
       <c r="N78" s="1" t="n"/>
@@ -3881,13 +3847,11 @@
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>269.31</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>269.24</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
@@ -3907,14 +3871,16 @@
       <c r="G79" s="1" t="n"/>
       <c r="H79" s="1" t="n"/>
       <c r="I79" s="1" t="n"/>
-      <c r="J79" s="1" t="n">
-        <v/>
+      <c r="J79" s="1" t="inlineStr">
+        <is>
+          <t>WBU</t>
+        </is>
       </c>
       <c r="K79" s="1" t="n"/>
       <c r="L79" s="1" t="n"/>
       <c r="M79" s="1" t="inlineStr">
         <is>
-          <t>SBU</t>
+          <t>WBU</t>
         </is>
       </c>
       <c r="N79" s="1" t="n"/>
@@ -3926,10 +3892,8 @@
           <t>358.63</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C80" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
@@ -3949,14 +3913,16 @@
       <c r="G80" s="1" t="n"/>
       <c r="H80" s="1" t="n"/>
       <c r="I80" s="1" t="n"/>
-      <c r="J80" s="1" t="n">
-        <v/>
+      <c r="J80" s="1" t="inlineStr">
+        <is>
+          <t>NBR</t>
+        </is>
       </c>
       <c r="K80" s="1" t="n"/>
       <c r="L80" s="1" t="n"/>
       <c r="M80" s="1" t="inlineStr">
         <is>
-          <t>WBR</t>
+          <t>NBR</t>
         </is>
       </c>
       <c r="N80" s="1" t="n"/>
@@ -3968,10 +3934,8 @@
           <t>358.63</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C81" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
@@ -3991,14 +3955,16 @@
       <c r="G81" s="1" t="n"/>
       <c r="H81" s="1" t="n"/>
       <c r="I81" s="1" t="n"/>
-      <c r="J81" s="1" t="n">
-        <v/>
+      <c r="J81" s="1" t="inlineStr">
+        <is>
+          <t>NBT</t>
+        </is>
       </c>
       <c r="K81" s="1" t="n"/>
       <c r="L81" s="1" t="n"/>
       <c r="M81" s="1" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>NBT</t>
         </is>
       </c>
       <c r="N81" s="1" t="n"/>
@@ -4010,10 +3976,8 @@
           <t>358.63</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C82" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
@@ -4033,14 +3997,16 @@
       <c r="G82" s="1" t="n"/>
       <c r="H82" s="1" t="n"/>
       <c r="I82" s="1" t="n"/>
-      <c r="J82" s="1" t="n">
-        <v/>
+      <c r="J82" s="1" t="inlineStr">
+        <is>
+          <t>NBL</t>
+        </is>
       </c>
       <c r="K82" s="1" t="n"/>
       <c r="L82" s="1" t="n"/>
       <c r="M82" s="1" t="inlineStr">
         <is>
-          <t>WBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="N82" s="1" t="n"/>
@@ -4052,10 +4018,8 @@
           <t>358.63</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C83" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
@@ -4075,14 +4039,16 @@
       <c r="G83" s="1" t="n"/>
       <c r="H83" s="1" t="n"/>
       <c r="I83" s="1" t="n"/>
-      <c r="J83" s="1" t="n">
-        <v/>
+      <c r="J83" s="1" t="inlineStr">
+        <is>
+          <t>NBU</t>
+        </is>
       </c>
       <c r="K83" s="1" t="n"/>
       <c r="L83" s="1" t="n"/>
       <c r="M83" s="1" t="inlineStr">
         <is>
-          <t>WBU</t>
+          <t>NBU</t>
         </is>
       </c>
       <c r="N83" s="1" t="n"/>
@@ -4098,10 +4064,8 @@
           <t>88.7</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C84" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
@@ -4120,33 +4084,33 @@
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>2915.xls</t>
+          <t>cluster_1655457007_1655457008_5913700311_5913700312_#4more</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>02172025</t>
+          <t>03112025</t>
         </is>
       </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>Bell Road and Hickory Hollow Terrace and Bell Forge Ln E</t>
+          <t>Clinton-Roosevelt</t>
         </is>
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>EBR</t>
         </is>
       </c>
       <c r="K84" s="1" t="n"/>
       <c r="L84" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>cluster_1655457007_1655457008_5913700311_5913700312_#4more</t>
         </is>
       </c>
       <c r="M84" s="1" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>EBR</t>
         </is>
       </c>
       <c r="N84" s="1" t="inlineStr">
@@ -4162,10 +4126,8 @@
           <t>88.7</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C85" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
@@ -4187,14 +4149,14 @@
       <c r="I85" s="1" t="n"/>
       <c r="J85" s="1" t="inlineStr">
         <is>
-          <t>NBT</t>
+          <t>EBT</t>
         </is>
       </c>
       <c r="K85" s="1" t="n"/>
       <c r="L85" s="1" t="n"/>
       <c r="M85" s="1" t="inlineStr">
         <is>
-          <t>NBT</t>
+          <t>EBT</t>
         </is>
       </c>
       <c r="N85" s="1" t="n"/>
@@ -4206,10 +4168,8 @@
           <t>88.7</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C86" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
@@ -4231,14 +4191,14 @@
       <c r="I86" s="1" t="n"/>
       <c r="J86" s="1" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="K86" s="1" t="n"/>
       <c r="L86" s="1" t="n"/>
       <c r="M86" s="1" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="N86" s="1" t="n"/>
@@ -4250,10 +4210,8 @@
           <t>88.7</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C87" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
@@ -4275,14 +4233,14 @@
       <c r="I87" s="1" t="n"/>
       <c r="J87" s="1" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>EBU</t>
         </is>
       </c>
       <c r="K87" s="1" t="n"/>
       <c r="L87" s="1" t="n"/>
       <c r="M87" s="1" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>EBU</t>
         </is>
       </c>
       <c r="N87" s="1" t="n"/>
@@ -4294,10 +4252,8 @@
           <t>179.57</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C88" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
@@ -4319,14 +4275,14 @@
       <c r="I88" s="1" t="n"/>
       <c r="J88" s="1" t="inlineStr">
         <is>
-          <t>EBR</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="K88" s="1" t="n"/>
       <c r="L88" s="1" t="n"/>
       <c r="M88" s="1" t="inlineStr">
         <is>
-          <t>EBR</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="N88" s="1" t="n"/>
@@ -4338,10 +4294,8 @@
           <t>179.57</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C89" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
@@ -4363,14 +4317,14 @@
       <c r="I89" s="1" t="n"/>
       <c r="J89" s="1" t="inlineStr">
         <is>
-          <t>EBT</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="K89" s="1" t="n"/>
       <c r="L89" s="1" t="n"/>
       <c r="M89" s="1" t="inlineStr">
         <is>
-          <t>EBT</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="N89" s="1" t="n"/>
@@ -4382,10 +4336,8 @@
           <t>179.57</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C90" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
@@ -4407,14 +4359,14 @@
       <c r="I90" s="1" t="n"/>
       <c r="J90" s="1" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="K90" s="1" t="n"/>
       <c r="L90" s="1" t="n"/>
       <c r="M90" s="1" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="N90" s="1" t="n"/>
@@ -4426,10 +4378,8 @@
           <t>179.57</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C91" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
@@ -4451,14 +4401,14 @@
       <c r="I91" s="1" t="n"/>
       <c r="J91" s="1" t="inlineStr">
         <is>
-          <t>EBU</t>
+          <t>SBU</t>
         </is>
       </c>
       <c r="K91" s="1" t="n"/>
       <c r="L91" s="1" t="n"/>
       <c r="M91" s="1" t="inlineStr">
         <is>
-          <t>EBU</t>
+          <t>SBU</t>
         </is>
       </c>
       <c r="N91" s="1" t="n"/>
@@ -4470,10 +4420,8 @@
           <t>269.35</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C92" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
@@ -4495,14 +4443,14 @@
       <c r="I92" s="1" t="n"/>
       <c r="J92" s="1" t="inlineStr">
         <is>
-          <t>SBR</t>
+          <t>WBR</t>
         </is>
       </c>
       <c r="K92" s="1" t="n"/>
       <c r="L92" s="1" t="n"/>
       <c r="M92" s="1" t="inlineStr">
         <is>
-          <t>SBR</t>
+          <t>WBR</t>
         </is>
       </c>
       <c r="N92" s="1" t="n"/>
@@ -4514,10 +4462,8 @@
           <t>269.35</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C93" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
@@ -4539,14 +4485,14 @@
       <c r="I93" s="1" t="n"/>
       <c r="J93" s="1" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="K93" s="1" t="n"/>
       <c r="L93" s="1" t="n"/>
       <c r="M93" s="1" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="N93" s="1" t="n"/>
@@ -4558,10 +4504,8 @@
           <t>269.35</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C94" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
@@ -4583,14 +4527,14 @@
       <c r="I94" s="1" t="n"/>
       <c r="J94" s="1" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>WBL</t>
         </is>
       </c>
       <c r="K94" s="1" t="n"/>
       <c r="L94" s="1" t="n"/>
       <c r="M94" s="1" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>WBL</t>
         </is>
       </c>
       <c r="N94" s="1" t="n"/>
@@ -4602,10 +4546,8 @@
           <t>269.35</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C95" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
@@ -4627,14 +4569,14 @@
       <c r="I95" s="1" t="n"/>
       <c r="J95" s="1" t="inlineStr">
         <is>
-          <t>SBU</t>
+          <t>WBU</t>
         </is>
       </c>
       <c r="K95" s="1" t="n"/>
       <c r="L95" s="1" t="n"/>
       <c r="M95" s="1" t="inlineStr">
         <is>
-          <t>SBU</t>
+          <t>WBU</t>
         </is>
       </c>
       <c r="N95" s="1" t="n"/>
@@ -4646,10 +4588,8 @@
           <t>358.74</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C96" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
@@ -4671,14 +4611,14 @@
       <c r="I96" s="1" t="n"/>
       <c r="J96" s="1" t="inlineStr">
         <is>
-          <t>WBR</t>
+          <t>NBR</t>
         </is>
       </c>
       <c r="K96" s="1" t="n"/>
       <c r="L96" s="1" t="n"/>
       <c r="M96" s="1" t="inlineStr">
         <is>
-          <t>WBR</t>
+          <t>NBR</t>
         </is>
       </c>
       <c r="N96" s="1" t="n"/>
@@ -4690,10 +4630,8 @@
           <t>358.74</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C97" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
@@ -4715,14 +4653,14 @@
       <c r="I97" s="1" t="n"/>
       <c r="J97" s="1" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>NBT</t>
         </is>
       </c>
       <c r="K97" s="1" t="n"/>
       <c r="L97" s="1" t="n"/>
       <c r="M97" s="1" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>NBT</t>
         </is>
       </c>
       <c r="N97" s="1" t="n"/>
@@ -4734,10 +4672,8 @@
           <t>358.74</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C98" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
@@ -4759,14 +4695,14 @@
       <c r="I98" s="1" t="n"/>
       <c r="J98" s="1" t="inlineStr">
         <is>
-          <t>WBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="K98" s="1" t="n"/>
       <c r="L98" s="1" t="n"/>
       <c r="M98" s="1" t="inlineStr">
         <is>
-          <t>WBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="N98" s="1" t="n"/>
@@ -4778,10 +4714,8 @@
           <t>358.74</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C99" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
@@ -4803,14 +4737,14 @@
       <c r="I99" s="1" t="n"/>
       <c r="J99" s="1" t="inlineStr">
         <is>
-          <t>WBU</t>
+          <t>NBU</t>
         </is>
       </c>
       <c r="K99" s="1" t="n"/>
       <c r="L99" s="1" t="n"/>
       <c r="M99" s="1" t="inlineStr">
         <is>
-          <t>WBU</t>
+          <t>NBU</t>
         </is>
       </c>
       <c r="N99" s="1" t="n"/>
@@ -4823,13 +4757,11 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>88.56</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -4846,8 +4778,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G100" s="1" t="n">
-        <v/>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>cluster_1679536346_9309565650</t>
+        </is>
       </c>
       <c r="H100" s="1" t="n">
         <v/>
@@ -4859,8 +4793,10 @@
         <v/>
       </c>
       <c r="K100" s="1" t="n"/>
-      <c r="L100" s="1" t="n">
-        <v/>
+      <c r="L100" s="1" t="inlineStr">
+        <is>
+          <t>cluster_1679536346_9309565650</t>
+        </is>
       </c>
       <c r="M100" s="1" t="n">
         <v/>
@@ -4875,13 +4811,11 @@
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>88.56</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
@@ -4915,13 +4849,11 @@
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>178.4</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>178.41</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
@@ -4955,13 +4887,11 @@
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>178.4</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t>178.41</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
@@ -4995,13 +4925,11 @@
       <c r="A104" s="1" t="n"/>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>358.43</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+          <t>358.45</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
@@ -5035,13 +4963,11 @@
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>358.43</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+          <t>358.45</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
@@ -5079,13 +5005,11 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>88.43</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>88.28</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
@@ -5102,22 +5026,30 @@
           <t>thru</t>
         </is>
       </c>
-      <c r="G106" s="1" t="n">
-        <v/>
-      </c>
-      <c r="H106" s="1" t="n">
-        <v/>
-      </c>
-      <c r="I106" s="1" t="n">
-        <v/>
-      </c>
-      <c r="J106" s="1" t="n">
-        <v/>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>cluster_1923791237_2203813886_2231137214_5913291209_#3more</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>03112025</t>
+        </is>
+      </c>
+      <c r="I106" s="1" t="inlineStr">
+        <is>
+          <t>Delano-Roosevelt</t>
+        </is>
+      </c>
+      <c r="J106" s="1" t="inlineStr">
+        <is>
+          <t>EBT</t>
+        </is>
       </c>
       <c r="K106" s="1" t="n"/>
       <c r="L106" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>cluster_1923791237_2203813886_2231137214_5913291209_#3more</t>
         </is>
       </c>
       <c r="M106" s="1" t="inlineStr">
@@ -5127,7 +5059,7 @@
       </c>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5135,13 +5067,11 @@
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>88.43</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>88.28</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
@@ -5161,8 +5091,10 @@
       <c r="G107" s="1" t="n"/>
       <c r="H107" s="1" t="n"/>
       <c r="I107" s="1" t="n"/>
-      <c r="J107" s="1" t="n">
-        <v/>
+      <c r="J107" s="1" t="inlineStr">
+        <is>
+          <t>EBL</t>
+        </is>
       </c>
       <c r="K107" s="1" t="n"/>
       <c r="L107" s="1" t="n"/>
@@ -5177,13 +5109,11 @@
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>88.43</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>88.28</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
@@ -5203,8 +5133,10 @@
       <c r="G108" s="1" t="n"/>
       <c r="H108" s="1" t="n"/>
       <c r="I108" s="1" t="n"/>
-      <c r="J108" s="1" t="n">
-        <v/>
+      <c r="J108" s="1" t="inlineStr">
+        <is>
+          <t>EBU</t>
+        </is>
       </c>
       <c r="K108" s="1" t="n"/>
       <c r="L108" s="1" t="n"/>
@@ -5219,13 +5151,11 @@
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>162.29</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>16</v>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
@@ -5245,8 +5175,10 @@
       <c r="G109" s="1" t="n"/>
       <c r="H109" s="1" t="n"/>
       <c r="I109" s="1" t="n"/>
-      <c r="J109" s="1" t="n">
-        <v/>
+      <c r="J109" s="1" t="inlineStr">
+        <is>
+          <t>SBR</t>
+        </is>
       </c>
       <c r="K109" s="1" t="n"/>
       <c r="L109" s="1" t="n"/>
@@ -5261,13 +5193,11 @@
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>162.29</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>16</v>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
@@ -5287,8 +5217,10 @@
       <c r="G110" s="1" t="n"/>
       <c r="H110" s="1" t="n"/>
       <c r="I110" s="1" t="n"/>
-      <c r="J110" s="1" t="n">
-        <v/>
+      <c r="J110" s="1" t="inlineStr">
+        <is>
+          <t>SBL</t>
+        </is>
       </c>
       <c r="K110" s="1" t="n"/>
       <c r="L110" s="1" t="n"/>
@@ -5303,13 +5235,11 @@
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>162.29</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>16</v>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
@@ -5329,14 +5259,16 @@
       <c r="G111" s="1" t="n"/>
       <c r="H111" s="1" t="n"/>
       <c r="I111" s="1" t="n"/>
-      <c r="J111" s="1" t="n">
-        <v/>
+      <c r="J111" s="1" t="inlineStr">
+        <is>
+          <t>SBL</t>
+        </is>
       </c>
       <c r="K111" s="1" t="n"/>
       <c r="L111" s="1" t="n"/>
       <c r="M111" s="1" t="inlineStr">
         <is>
-          <t>SBU</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="N111" s="1" t="n"/>
@@ -5348,10 +5280,8 @@
           <t>268.55</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C112" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
@@ -5371,8 +5301,10 @@
       <c r="G112" s="1" t="n"/>
       <c r="H112" s="1" t="n"/>
       <c r="I112" s="1" t="n"/>
-      <c r="J112" s="1" t="n">
-        <v/>
+      <c r="J112" s="1" t="inlineStr">
+        <is>
+          <t>WBR</t>
+        </is>
       </c>
       <c r="K112" s="1" t="n"/>
       <c r="L112" s="1" t="n"/>
@@ -5390,10 +5322,8 @@
           <t>268.55</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C113" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
@@ -5413,8 +5343,10 @@
       <c r="G113" s="1" t="n"/>
       <c r="H113" s="1" t="n"/>
       <c r="I113" s="1" t="n"/>
-      <c r="J113" s="1" t="n">
-        <v/>
+      <c r="J113" s="1" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
       </c>
       <c r="K113" s="1" t="n"/>
       <c r="L113" s="1" t="n"/>
@@ -5433,13 +5365,11 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>92.72</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>93.45</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
@@ -5456,8 +5386,10 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G114" s="1" t="n">
-        <v/>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>cluster_1961538074_9672052329</t>
+        </is>
       </c>
       <c r="H114" s="1" t="n">
         <v/>
@@ -5469,8 +5401,10 @@
         <v/>
       </c>
       <c r="K114" s="1" t="n"/>
-      <c r="L114" s="1" t="n">
-        <v/>
+      <c r="L114" s="1" t="inlineStr">
+        <is>
+          <t>cluster_1961538074_9672052329</t>
+        </is>
       </c>
       <c r="M114" s="1" t="n">
         <v/>
@@ -5485,13 +5419,11 @@
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>92.72</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>93.45</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
@@ -5528,10 +5460,8 @@
           <t>359.04</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C116" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
@@ -5572,10 +5502,8 @@
           <t>89.17</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C117" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
@@ -5592,32 +5520,40 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G117" s="1" t="n">
-        <v/>
-      </c>
-      <c r="H117" s="1" t="n">
-        <v/>
-      </c>
-      <c r="I117" s="1" t="n">
-        <v/>
-      </c>
-      <c r="J117" s="1" t="n">
-        <v/>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>cluster_2565193678_2565193679_256631215_2817519892_#8more</t>
+        </is>
+      </c>
+      <c r="H117" s="1" t="inlineStr">
+        <is>
+          <t>03112025</t>
+        </is>
+      </c>
+      <c r="I117" s="1" t="inlineStr">
+        <is>
+          <t>State-Roosevelt</t>
+        </is>
+      </c>
+      <c r="J117" s="1" t="inlineStr">
+        <is>
+          <t>EBR</t>
+        </is>
       </c>
       <c r="K117" s="1" t="n"/>
       <c r="L117" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>cluster_2565193678_2565193679_256631215_2817519892_#8more</t>
         </is>
       </c>
       <c r="M117" s="1" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>EBR</t>
         </is>
       </c>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -5628,10 +5564,8 @@
           <t>89.17</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C118" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
@@ -5651,14 +5585,16 @@
       <c r="G118" s="1" t="n"/>
       <c r="H118" s="1" t="n"/>
       <c r="I118" s="1" t="n"/>
-      <c r="J118" s="1" t="n">
-        <v/>
+      <c r="J118" s="1" t="inlineStr">
+        <is>
+          <t>EBT</t>
+        </is>
       </c>
       <c r="K118" s="1" t="n"/>
       <c r="L118" s="1" t="n"/>
       <c r="M118" s="1" t="inlineStr">
         <is>
-          <t>NBT</t>
+          <t>EBT</t>
         </is>
       </c>
       <c r="N118" s="1" t="n"/>
@@ -5670,10 +5606,8 @@
           <t>89.17</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C119" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
@@ -5693,14 +5627,16 @@
       <c r="G119" s="1" t="n"/>
       <c r="H119" s="1" t="n"/>
       <c r="I119" s="1" t="n"/>
-      <c r="J119" s="1" t="n">
-        <v/>
+      <c r="J119" s="1" t="inlineStr">
+        <is>
+          <t>EBL</t>
+        </is>
       </c>
       <c r="K119" s="1" t="n"/>
       <c r="L119" s="1" t="n"/>
       <c r="M119" s="1" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="N119" s="1" t="n"/>
@@ -5712,10 +5648,8 @@
           <t>89.17</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C120" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
@@ -5735,14 +5669,16 @@
       <c r="G120" s="1" t="n"/>
       <c r="H120" s="1" t="n"/>
       <c r="I120" s="1" t="n"/>
-      <c r="J120" s="1" t="n">
-        <v/>
+      <c r="J120" s="1" t="inlineStr">
+        <is>
+          <t>EBU</t>
+        </is>
       </c>
       <c r="K120" s="1" t="n"/>
       <c r="L120" s="1" t="n"/>
       <c r="M120" s="1" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>EBU</t>
         </is>
       </c>
       <c r="N120" s="1" t="n"/>
@@ -5754,10 +5690,8 @@
           <t>179.96</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C121" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
@@ -5777,14 +5711,16 @@
       <c r="G121" s="1" t="n"/>
       <c r="H121" s="1" t="n"/>
       <c r="I121" s="1" t="n"/>
-      <c r="J121" s="1" t="n">
-        <v/>
+      <c r="J121" s="1" t="inlineStr">
+        <is>
+          <t>SBR</t>
+        </is>
       </c>
       <c r="K121" s="1" t="n"/>
       <c r="L121" s="1" t="n"/>
       <c r="M121" s="1" t="inlineStr">
         <is>
-          <t>EBR</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="N121" s="1" t="n"/>
@@ -5796,10 +5732,8 @@
           <t>179.96</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C122" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
@@ -5819,14 +5753,16 @@
       <c r="G122" s="1" t="n"/>
       <c r="H122" s="1" t="n"/>
       <c r="I122" s="1" t="n"/>
-      <c r="J122" s="1" t="n">
-        <v/>
+      <c r="J122" s="1" t="inlineStr">
+        <is>
+          <t>SBT</t>
+        </is>
       </c>
       <c r="K122" s="1" t="n"/>
       <c r="L122" s="1" t="n"/>
       <c r="M122" s="1" t="inlineStr">
         <is>
-          <t>EBT</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="N122" s="1" t="n"/>
@@ -5838,10 +5774,8 @@
           <t>179.96</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C123" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
@@ -5861,14 +5795,16 @@
       <c r="G123" s="1" t="n"/>
       <c r="H123" s="1" t="n"/>
       <c r="I123" s="1" t="n"/>
-      <c r="J123" s="1" t="n">
-        <v/>
+      <c r="J123" s="1" t="inlineStr">
+        <is>
+          <t>SBL</t>
+        </is>
       </c>
       <c r="K123" s="1" t="n"/>
       <c r="L123" s="1" t="n"/>
       <c r="M123" s="1" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="N123" s="1" t="n"/>
@@ -5880,10 +5816,8 @@
           <t>179.96</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C124" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
@@ -5903,14 +5837,16 @@
       <c r="G124" s="1" t="n"/>
       <c r="H124" s="1" t="n"/>
       <c r="I124" s="1" t="n"/>
-      <c r="J124" s="1" t="n">
-        <v/>
+      <c r="J124" s="1" t="inlineStr">
+        <is>
+          <t>SBU</t>
+        </is>
       </c>
       <c r="K124" s="1" t="n"/>
       <c r="L124" s="1" t="n"/>
       <c r="M124" s="1" t="inlineStr">
         <is>
-          <t>EBU</t>
+          <t>SBU</t>
         </is>
       </c>
       <c r="N124" s="1" t="n"/>
@@ -5922,10 +5858,8 @@
           <t>268.5</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C125" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
@@ -5945,14 +5879,16 @@
       <c r="G125" s="1" t="n"/>
       <c r="H125" s="1" t="n"/>
       <c r="I125" s="1" t="n"/>
-      <c r="J125" s="1" t="n">
-        <v/>
+      <c r="J125" s="1" t="inlineStr">
+        <is>
+          <t>WBR</t>
+        </is>
       </c>
       <c r="K125" s="1" t="n"/>
       <c r="L125" s="1" t="n"/>
       <c r="M125" s="1" t="inlineStr">
         <is>
-          <t>SBR</t>
+          <t>WBR</t>
         </is>
       </c>
       <c r="N125" s="1" t="n"/>
@@ -5964,10 +5900,8 @@
           <t>268.5</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C126" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
@@ -5987,14 +5921,16 @@
       <c r="G126" s="1" t="n"/>
       <c r="H126" s="1" t="n"/>
       <c r="I126" s="1" t="n"/>
-      <c r="J126" s="1" t="n">
-        <v/>
+      <c r="J126" s="1" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
       </c>
       <c r="K126" s="1" t="n"/>
       <c r="L126" s="1" t="n"/>
       <c r="M126" s="1" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="N126" s="1" t="n"/>
@@ -6006,10 +5942,8 @@
           <t>268.5</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C127" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
@@ -6029,14 +5963,16 @@
       <c r="G127" s="1" t="n"/>
       <c r="H127" s="1" t="n"/>
       <c r="I127" s="1" t="n"/>
-      <c r="J127" s="1" t="n">
-        <v/>
+      <c r="J127" s="1" t="inlineStr">
+        <is>
+          <t>WBL</t>
+        </is>
       </c>
       <c r="K127" s="1" t="n"/>
       <c r="L127" s="1" t="n"/>
       <c r="M127" s="1" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>WBL</t>
         </is>
       </c>
       <c r="N127" s="1" t="n"/>
@@ -6048,10 +5984,8 @@
           <t>268.5</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C128" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
@@ -6071,14 +6005,16 @@
       <c r="G128" s="1" t="n"/>
       <c r="H128" s="1" t="n"/>
       <c r="I128" s="1" t="n"/>
-      <c r="J128" s="1" t="n">
-        <v/>
+      <c r="J128" s="1" t="inlineStr">
+        <is>
+          <t>WBU</t>
+        </is>
       </c>
       <c r="K128" s="1" t="n"/>
       <c r="L128" s="1" t="n"/>
       <c r="M128" s="1" t="inlineStr">
         <is>
-          <t>SBU</t>
+          <t>WBU</t>
         </is>
       </c>
       <c r="N128" s="1" t="n"/>
@@ -6090,10 +6026,8 @@
           <t>358.52</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C129" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
@@ -6113,14 +6047,16 @@
       <c r="G129" s="1" t="n"/>
       <c r="H129" s="1" t="n"/>
       <c r="I129" s="1" t="n"/>
-      <c r="J129" s="1" t="n">
-        <v/>
+      <c r="J129" s="1" t="inlineStr">
+        <is>
+          <t>NBR</t>
+        </is>
       </c>
       <c r="K129" s="1" t="n"/>
       <c r="L129" s="1" t="n"/>
       <c r="M129" s="1" t="inlineStr">
         <is>
-          <t>WBR</t>
+          <t>NBR</t>
         </is>
       </c>
       <c r="N129" s="1" t="n"/>
@@ -6132,10 +6068,8 @@
           <t>358.52</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C130" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
@@ -6155,14 +6089,16 @@
       <c r="G130" s="1" t="n"/>
       <c r="H130" s="1" t="n"/>
       <c r="I130" s="1" t="n"/>
-      <c r="J130" s="1" t="n">
-        <v/>
+      <c r="J130" s="1" t="inlineStr">
+        <is>
+          <t>NBT</t>
+        </is>
       </c>
       <c r="K130" s="1" t="n"/>
       <c r="L130" s="1" t="n"/>
       <c r="M130" s="1" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>NBT</t>
         </is>
       </c>
       <c r="N130" s="1" t="n"/>
@@ -6174,10 +6110,8 @@
           <t>358.52</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C131" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
@@ -6197,14 +6131,16 @@
       <c r="G131" s="1" t="n"/>
       <c r="H131" s="1" t="n"/>
       <c r="I131" s="1" t="n"/>
-      <c r="J131" s="1" t="n">
-        <v/>
+      <c r="J131" s="1" t="inlineStr">
+        <is>
+          <t>NBL</t>
+        </is>
       </c>
       <c r="K131" s="1" t="n"/>
       <c r="L131" s="1" t="n"/>
       <c r="M131" s="1" t="inlineStr">
         <is>
-          <t>WBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="N131" s="1" t="n"/>
@@ -6216,10 +6152,8 @@
           <t>358.52</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C132" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
@@ -6239,14 +6173,16 @@
       <c r="G132" s="1" t="n"/>
       <c r="H132" s="1" t="n"/>
       <c r="I132" s="1" t="n"/>
-      <c r="J132" s="1" t="n">
-        <v/>
+      <c r="J132" s="1" t="inlineStr">
+        <is>
+          <t>NBU</t>
+        </is>
       </c>
       <c r="K132" s="1" t="n"/>
       <c r="L132" s="1" t="n"/>
       <c r="M132" s="1" t="inlineStr">
         <is>
-          <t>WBU</t>
+          <t>NBU</t>
         </is>
       </c>
       <c r="N132" s="1" t="n"/>
@@ -6262,10 +6198,8 @@
           <t>88.44</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C133" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
@@ -6282,32 +6216,40 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G133" s="1" t="n">
-        <v/>
-      </c>
-      <c r="H133" s="1" t="n">
-        <v/>
-      </c>
-      <c r="I133" s="1" t="n">
-        <v/>
-      </c>
-      <c r="J133" s="1" t="n">
-        <v/>
+      <c r="G133" s="1" t="inlineStr">
+        <is>
+          <t>cluster_2787305554_2787305555_2787305601_2787305603_#7more</t>
+        </is>
+      </c>
+      <c r="H133" s="1" t="inlineStr">
+        <is>
+          <t>03112025</t>
+        </is>
+      </c>
+      <c r="I133" s="1" t="inlineStr">
+        <is>
+          <t>Michigan-Rooseve</t>
+        </is>
+      </c>
+      <c r="J133" s="1" t="inlineStr">
+        <is>
+          <t>EBR</t>
+        </is>
       </c>
       <c r="K133" s="1" t="n"/>
       <c r="L133" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>cluster_2787305554_2787305555_2787305601_2787305603_#7more</t>
         </is>
       </c>
       <c r="M133" s="1" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>EBR</t>
         </is>
       </c>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -6318,10 +6260,8 @@
           <t>88.44</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C134" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
@@ -6341,14 +6281,16 @@
       <c r="G134" s="1" t="n"/>
       <c r="H134" s="1" t="n"/>
       <c r="I134" s="1" t="n"/>
-      <c r="J134" s="1" t="n">
-        <v/>
+      <c r="J134" s="1" t="inlineStr">
+        <is>
+          <t>EBT</t>
+        </is>
       </c>
       <c r="K134" s="1" t="n"/>
       <c r="L134" s="1" t="n"/>
       <c r="M134" s="1" t="inlineStr">
         <is>
-          <t>NBT</t>
+          <t>EBT</t>
         </is>
       </c>
       <c r="N134" s="1" t="n"/>
@@ -6360,10 +6302,8 @@
           <t>88.44</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C135" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -6383,14 +6323,16 @@
       <c r="G135" s="1" t="n"/>
       <c r="H135" s="1" t="n"/>
       <c r="I135" s="1" t="n"/>
-      <c r="J135" s="1" t="n">
-        <v/>
+      <c r="J135" s="1" t="inlineStr">
+        <is>
+          <t>EBL</t>
+        </is>
       </c>
       <c r="K135" s="1" t="n"/>
       <c r="L135" s="1" t="n"/>
       <c r="M135" s="1" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="N135" s="1" t="n"/>
@@ -6402,10 +6344,8 @@
           <t>88.44</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C136" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
@@ -6425,14 +6365,16 @@
       <c r="G136" s="1" t="n"/>
       <c r="H136" s="1" t="n"/>
       <c r="I136" s="1" t="n"/>
-      <c r="J136" s="1" t="n">
-        <v/>
+      <c r="J136" s="1" t="inlineStr">
+        <is>
+          <t>EBU</t>
+        </is>
       </c>
       <c r="K136" s="1" t="n"/>
       <c r="L136" s="1" t="n"/>
       <c r="M136" s="1" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>EBU</t>
         </is>
       </c>
       <c r="N136" s="1" t="n"/>
@@ -6444,10 +6386,8 @@
           <t>179.92</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C137" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
@@ -6467,14 +6407,16 @@
       <c r="G137" s="1" t="n"/>
       <c r="H137" s="1" t="n"/>
       <c r="I137" s="1" t="n"/>
-      <c r="J137" s="1" t="n">
-        <v/>
+      <c r="J137" s="1" t="inlineStr">
+        <is>
+          <t>SBR</t>
+        </is>
       </c>
       <c r="K137" s="1" t="n"/>
       <c r="L137" s="1" t="n"/>
       <c r="M137" s="1" t="inlineStr">
         <is>
-          <t>EBR</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="N137" s="1" t="n"/>
@@ -6486,10 +6428,8 @@
           <t>179.92</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C138" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
@@ -6509,14 +6449,16 @@
       <c r="G138" s="1" t="n"/>
       <c r="H138" s="1" t="n"/>
       <c r="I138" s="1" t="n"/>
-      <c r="J138" s="1" t="n">
-        <v/>
+      <c r="J138" s="1" t="inlineStr">
+        <is>
+          <t>SBT</t>
+        </is>
       </c>
       <c r="K138" s="1" t="n"/>
       <c r="L138" s="1" t="n"/>
       <c r="M138" s="1" t="inlineStr">
         <is>
-          <t>EBT</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="N138" s="1" t="n"/>
@@ -6528,10 +6470,8 @@
           <t>179.92</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C139" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
@@ -6551,14 +6491,16 @@
       <c r="G139" s="1" t="n"/>
       <c r="H139" s="1" t="n"/>
       <c r="I139" s="1" t="n"/>
-      <c r="J139" s="1" t="n">
-        <v/>
+      <c r="J139" s="1" t="inlineStr">
+        <is>
+          <t>SBL</t>
+        </is>
       </c>
       <c r="K139" s="1" t="n"/>
       <c r="L139" s="1" t="n"/>
       <c r="M139" s="1" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="N139" s="1" t="n"/>
@@ -6570,10 +6512,8 @@
           <t>179.92</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C140" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
@@ -6593,14 +6533,16 @@
       <c r="G140" s="1" t="n"/>
       <c r="H140" s="1" t="n"/>
       <c r="I140" s="1" t="n"/>
-      <c r="J140" s="1" t="n">
-        <v/>
+      <c r="J140" s="1" t="inlineStr">
+        <is>
+          <t>SBU</t>
+        </is>
       </c>
       <c r="K140" s="1" t="n"/>
       <c r="L140" s="1" t="n"/>
       <c r="M140" s="1" t="inlineStr">
         <is>
-          <t>EBU</t>
+          <t>SBU</t>
         </is>
       </c>
       <c r="N140" s="1" t="n"/>
@@ -6612,10 +6554,8 @@
           <t>269.05</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C141" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
@@ -6635,14 +6575,16 @@
       <c r="G141" s="1" t="n"/>
       <c r="H141" s="1" t="n"/>
       <c r="I141" s="1" t="n"/>
-      <c r="J141" s="1" t="n">
-        <v/>
+      <c r="J141" s="1" t="inlineStr">
+        <is>
+          <t>WBR</t>
+        </is>
       </c>
       <c r="K141" s="1" t="n"/>
       <c r="L141" s="1" t="n"/>
       <c r="M141" s="1" t="inlineStr">
         <is>
-          <t>SBR</t>
+          <t>WBR</t>
         </is>
       </c>
       <c r="N141" s="1" t="n"/>
@@ -6654,10 +6596,8 @@
           <t>269.05</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C142" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
@@ -6677,14 +6617,16 @@
       <c r="G142" s="1" t="n"/>
       <c r="H142" s="1" t="n"/>
       <c r="I142" s="1" t="n"/>
-      <c r="J142" s="1" t="n">
-        <v/>
+      <c r="J142" s="1" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
       </c>
       <c r="K142" s="1" t="n"/>
       <c r="L142" s="1" t="n"/>
       <c r="M142" s="1" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="N142" s="1" t="n"/>
@@ -6696,10 +6638,8 @@
           <t>269.05</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C143" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
@@ -6719,14 +6659,16 @@
       <c r="G143" s="1" t="n"/>
       <c r="H143" s="1" t="n"/>
       <c r="I143" s="1" t="n"/>
-      <c r="J143" s="1" t="n">
-        <v/>
+      <c r="J143" s="1" t="inlineStr">
+        <is>
+          <t>WBL</t>
+        </is>
       </c>
       <c r="K143" s="1" t="n"/>
       <c r="L143" s="1" t="n"/>
       <c r="M143" s="1" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>WBL</t>
         </is>
       </c>
       <c r="N143" s="1" t="n"/>
@@ -6738,10 +6680,8 @@
           <t>269.05</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C144" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
@@ -6761,14 +6701,16 @@
       <c r="G144" s="1" t="n"/>
       <c r="H144" s="1" t="n"/>
       <c r="I144" s="1" t="n"/>
-      <c r="J144" s="1" t="n">
-        <v/>
+      <c r="J144" s="1" t="inlineStr">
+        <is>
+          <t>WBU</t>
+        </is>
       </c>
       <c r="K144" s="1" t="n"/>
       <c r="L144" s="1" t="n"/>
       <c r="M144" s="1" t="inlineStr">
         <is>
-          <t>SBU</t>
+          <t>WBU</t>
         </is>
       </c>
       <c r="N144" s="1" t="n"/>
@@ -6780,10 +6722,8 @@
           <t>359.26</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C145" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
@@ -6803,14 +6743,16 @@
       <c r="G145" s="1" t="n"/>
       <c r="H145" s="1" t="n"/>
       <c r="I145" s="1" t="n"/>
-      <c r="J145" s="1" t="n">
-        <v/>
+      <c r="J145" s="1" t="inlineStr">
+        <is>
+          <t>NBR</t>
+        </is>
       </c>
       <c r="K145" s="1" t="n"/>
       <c r="L145" s="1" t="n"/>
       <c r="M145" s="1" t="inlineStr">
         <is>
-          <t>WBR</t>
+          <t>NBR</t>
         </is>
       </c>
       <c r="N145" s="1" t="n"/>
@@ -6822,10 +6764,8 @@
           <t>359.26</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C146" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
@@ -6845,14 +6785,16 @@
       <c r="G146" s="1" t="n"/>
       <c r="H146" s="1" t="n"/>
       <c r="I146" s="1" t="n"/>
-      <c r="J146" s="1" t="n">
-        <v/>
+      <c r="J146" s="1" t="inlineStr">
+        <is>
+          <t>NBT</t>
+        </is>
       </c>
       <c r="K146" s="1" t="n"/>
       <c r="L146" s="1" t="n"/>
       <c r="M146" s="1" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>NBT</t>
         </is>
       </c>
       <c r="N146" s="1" t="n"/>
@@ -6864,10 +6806,8 @@
           <t>359.26</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C147" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
@@ -6887,14 +6827,16 @@
       <c r="G147" s="1" t="n"/>
       <c r="H147" s="1" t="n"/>
       <c r="I147" s="1" t="n"/>
-      <c r="J147" s="1" t="n">
-        <v/>
+      <c r="J147" s="1" t="inlineStr">
+        <is>
+          <t>NBL</t>
+        </is>
       </c>
       <c r="K147" s="1" t="n"/>
       <c r="L147" s="1" t="n"/>
       <c r="M147" s="1" t="inlineStr">
         <is>
-          <t>WBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="N147" s="1" t="n"/>
@@ -6906,10 +6848,8 @@
           <t>359.26</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C148" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
@@ -6929,14 +6869,16 @@
       <c r="G148" s="1" t="n"/>
       <c r="H148" s="1" t="n"/>
       <c r="I148" s="1" t="n"/>
-      <c r="J148" s="1" t="n">
-        <v/>
+      <c r="J148" s="1" t="inlineStr">
+        <is>
+          <t>NBU</t>
+        </is>
       </c>
       <c r="K148" s="1" t="n"/>
       <c r="L148" s="1" t="n"/>
       <c r="M148" s="1" t="inlineStr">
         <is>
-          <t>WBU</t>
+          <t>NBU</t>
         </is>
       </c>
       <c r="N148" s="1" t="n"/>
@@ -6949,13 +6891,11 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>88.87</t>
-        </is>
-      </c>
-      <c r="C149" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
@@ -6972,32 +6912,40 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G149" s="1" t="n">
-        <v/>
-      </c>
-      <c r="H149" s="1" t="n">
-        <v/>
-      </c>
-      <c r="I149" s="1" t="n">
-        <v/>
-      </c>
-      <c r="J149" s="1" t="n">
-        <v/>
+      <c r="G149" s="1" t="inlineStr">
+        <is>
+          <t>cluster_33781534_4806706815_4806706816_4806706819_#4more</t>
+        </is>
+      </c>
+      <c r="H149" s="1" t="inlineStr">
+        <is>
+          <t>03112025</t>
+        </is>
+      </c>
+      <c r="I149" s="1" t="inlineStr">
+        <is>
+          <t>Wabash-Roosevelt</t>
+        </is>
+      </c>
+      <c r="J149" s="1" t="inlineStr">
+        <is>
+          <t>EBR</t>
+        </is>
       </c>
       <c r="K149" s="1" t="n"/>
       <c r="L149" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>cluster_33781534_4806706815_4806706816_4806706819_#4more</t>
         </is>
       </c>
       <c r="M149" s="1" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>EBR</t>
         </is>
       </c>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -7005,13 +6953,11 @@
       <c r="A150" s="1" t="n"/>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>88.87</t>
-        </is>
-      </c>
-      <c r="C150" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
@@ -7031,14 +6977,16 @@
       <c r="G150" s="1" t="n"/>
       <c r="H150" s="1" t="n"/>
       <c r="I150" s="1" t="n"/>
-      <c r="J150" s="1" t="n">
-        <v/>
+      <c r="J150" s="1" t="inlineStr">
+        <is>
+          <t>EBT</t>
+        </is>
       </c>
       <c r="K150" s="1" t="n"/>
       <c r="L150" s="1" t="n"/>
       <c r="M150" s="1" t="inlineStr">
         <is>
-          <t>NBT</t>
+          <t>EBT</t>
         </is>
       </c>
       <c r="N150" s="1" t="n"/>
@@ -7047,13 +6995,11 @@
       <c r="A151" s="1" t="n"/>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>88.87</t>
-        </is>
-      </c>
-      <c r="C151" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
@@ -7073,14 +7019,16 @@
       <c r="G151" s="1" t="n"/>
       <c r="H151" s="1" t="n"/>
       <c r="I151" s="1" t="n"/>
-      <c r="J151" s="1" t="n">
-        <v/>
+      <c r="J151" s="1" t="inlineStr">
+        <is>
+          <t>EBL</t>
+        </is>
       </c>
       <c r="K151" s="1" t="n"/>
       <c r="L151" s="1" t="n"/>
       <c r="M151" s="1" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="N151" s="1" t="n"/>
@@ -7089,13 +7037,11 @@
       <c r="A152" s="1" t="n"/>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>88.87</t>
-        </is>
-      </c>
-      <c r="C152" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
@@ -7115,14 +7061,16 @@
       <c r="G152" s="1" t="n"/>
       <c r="H152" s="1" t="n"/>
       <c r="I152" s="1" t="n"/>
-      <c r="J152" s="1" t="n">
-        <v/>
+      <c r="J152" s="1" t="inlineStr">
+        <is>
+          <t>EBU</t>
+        </is>
       </c>
       <c r="K152" s="1" t="n"/>
       <c r="L152" s="1" t="n"/>
       <c r="M152" s="1" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>EBU</t>
         </is>
       </c>
       <c r="N152" s="1" t="n"/>
@@ -7134,10 +7082,8 @@
           <t>179.45</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C153" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
@@ -7157,14 +7103,16 @@
       <c r="G153" s="1" t="n"/>
       <c r="H153" s="1" t="n"/>
       <c r="I153" s="1" t="n"/>
-      <c r="J153" s="1" t="n">
-        <v/>
+      <c r="J153" s="1" t="inlineStr">
+        <is>
+          <t>SBR</t>
+        </is>
       </c>
       <c r="K153" s="1" t="n"/>
       <c r="L153" s="1" t="n"/>
       <c r="M153" s="1" t="inlineStr">
         <is>
-          <t>EBR</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="N153" s="1" t="n"/>
@@ -7176,10 +7124,8 @@
           <t>179.45</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C154" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
@@ -7199,14 +7145,16 @@
       <c r="G154" s="1" t="n"/>
       <c r="H154" s="1" t="n"/>
       <c r="I154" s="1" t="n"/>
-      <c r="J154" s="1" t="n">
-        <v/>
+      <c r="J154" s="1" t="inlineStr">
+        <is>
+          <t>SBT</t>
+        </is>
       </c>
       <c r="K154" s="1" t="n"/>
       <c r="L154" s="1" t="n"/>
       <c r="M154" s="1" t="inlineStr">
         <is>
-          <t>EBT</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="N154" s="1" t="n"/>
@@ -7218,10 +7166,8 @@
           <t>179.45</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C155" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
@@ -7241,14 +7187,16 @@
       <c r="G155" s="1" t="n"/>
       <c r="H155" s="1" t="n"/>
       <c r="I155" s="1" t="n"/>
-      <c r="J155" s="1" t="n">
-        <v/>
+      <c r="J155" s="1" t="inlineStr">
+        <is>
+          <t>SBL</t>
+        </is>
       </c>
       <c r="K155" s="1" t="n"/>
       <c r="L155" s="1" t="n"/>
       <c r="M155" s="1" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="N155" s="1" t="n"/>
@@ -7260,10 +7208,8 @@
           <t>179.45</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C156" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
@@ -7283,14 +7229,16 @@
       <c r="G156" s="1" t="n"/>
       <c r="H156" s="1" t="n"/>
       <c r="I156" s="1" t="n"/>
-      <c r="J156" s="1" t="n">
-        <v/>
+      <c r="J156" s="1" t="inlineStr">
+        <is>
+          <t>SBU</t>
+        </is>
       </c>
       <c r="K156" s="1" t="n"/>
       <c r="L156" s="1" t="n"/>
       <c r="M156" s="1" t="inlineStr">
         <is>
-          <t>EBU</t>
+          <t>SBU</t>
         </is>
       </c>
       <c r="N156" s="1" t="n"/>
@@ -7302,10 +7250,8 @@
           <t>269.98</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C157" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
@@ -7325,14 +7271,16 @@
       <c r="G157" s="1" t="n"/>
       <c r="H157" s="1" t="n"/>
       <c r="I157" s="1" t="n"/>
-      <c r="J157" s="1" t="n">
-        <v/>
+      <c r="J157" s="1" t="inlineStr">
+        <is>
+          <t>WBR</t>
+        </is>
       </c>
       <c r="K157" s="1" t="n"/>
       <c r="L157" s="1" t="n"/>
       <c r="M157" s="1" t="inlineStr">
         <is>
-          <t>SBR</t>
+          <t>WBR</t>
         </is>
       </c>
       <c r="N157" s="1" t="n"/>
@@ -7344,10 +7292,8 @@
           <t>269.98</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C158" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
@@ -7367,14 +7313,16 @@
       <c r="G158" s="1" t="n"/>
       <c r="H158" s="1" t="n"/>
       <c r="I158" s="1" t="n"/>
-      <c r="J158" s="1" t="n">
-        <v/>
+      <c r="J158" s="1" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
       </c>
       <c r="K158" s="1" t="n"/>
       <c r="L158" s="1" t="n"/>
       <c r="M158" s="1" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="N158" s="1" t="n"/>
@@ -7386,10 +7334,8 @@
           <t>269.98</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C159" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
@@ -7409,14 +7355,16 @@
       <c r="G159" s="1" t="n"/>
       <c r="H159" s="1" t="n"/>
       <c r="I159" s="1" t="n"/>
-      <c r="J159" s="1" t="n">
-        <v/>
+      <c r="J159" s="1" t="inlineStr">
+        <is>
+          <t>WBL</t>
+        </is>
       </c>
       <c r="K159" s="1" t="n"/>
       <c r="L159" s="1" t="n"/>
       <c r="M159" s="1" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>WBL</t>
         </is>
       </c>
       <c r="N159" s="1" t="n"/>
@@ -7428,10 +7376,8 @@
           <t>269.98</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="C160" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
@@ -7451,14 +7397,16 @@
       <c r="G160" s="1" t="n"/>
       <c r="H160" s="1" t="n"/>
       <c r="I160" s="1" t="n"/>
-      <c r="J160" s="1" t="n">
-        <v/>
+      <c r="J160" s="1" t="inlineStr">
+        <is>
+          <t>WBU</t>
+        </is>
       </c>
       <c r="K160" s="1" t="n"/>
       <c r="L160" s="1" t="n"/>
       <c r="M160" s="1" t="inlineStr">
         <is>
-          <t>SBU</t>
+          <t>WBU</t>
         </is>
       </c>
       <c r="N160" s="1" t="n"/>
@@ -7470,10 +7418,8 @@
           <t>359.12</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C161" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
@@ -7493,14 +7439,16 @@
       <c r="G161" s="1" t="n"/>
       <c r="H161" s="1" t="n"/>
       <c r="I161" s="1" t="n"/>
-      <c r="J161" s="1" t="n">
-        <v/>
+      <c r="J161" s="1" t="inlineStr">
+        <is>
+          <t>NBR</t>
+        </is>
       </c>
       <c r="K161" s="1" t="n"/>
       <c r="L161" s="1" t="n"/>
       <c r="M161" s="1" t="inlineStr">
         <is>
-          <t>WBR</t>
+          <t>NBR</t>
         </is>
       </c>
       <c r="N161" s="1" t="n"/>
@@ -7512,10 +7460,8 @@
           <t>359.12</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C162" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
@@ -7535,14 +7481,16 @@
       <c r="G162" s="1" t="n"/>
       <c r="H162" s="1" t="n"/>
       <c r="I162" s="1" t="n"/>
-      <c r="J162" s="1" t="n">
-        <v/>
+      <c r="J162" s="1" t="inlineStr">
+        <is>
+          <t>NBT</t>
+        </is>
       </c>
       <c r="K162" s="1" t="n"/>
       <c r="L162" s="1" t="n"/>
       <c r="M162" s="1" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>NBT</t>
         </is>
       </c>
       <c r="N162" s="1" t="n"/>
@@ -7554,10 +7502,8 @@
           <t>359.12</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C163" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
@@ -7577,14 +7523,16 @@
       <c r="G163" s="1" t="n"/>
       <c r="H163" s="1" t="n"/>
       <c r="I163" s="1" t="n"/>
-      <c r="J163" s="1" t="n">
-        <v/>
+      <c r="J163" s="1" t="inlineStr">
+        <is>
+          <t>NBL</t>
+        </is>
       </c>
       <c r="K163" s="1" t="n"/>
       <c r="L163" s="1" t="n"/>
       <c r="M163" s="1" t="inlineStr">
         <is>
-          <t>WBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="N163" s="1" t="n"/>
@@ -7596,10 +7544,8 @@
           <t>359.12</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="C164" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
@@ -7619,14 +7565,16 @@
       <c r="G164" s="1" t="n"/>
       <c r="H164" s="1" t="n"/>
       <c r="I164" s="1" t="n"/>
-      <c r="J164" s="1" t="n">
-        <v/>
+      <c r="J164" s="1" t="inlineStr">
+        <is>
+          <t>NBU</t>
+        </is>
       </c>
       <c r="K164" s="1" t="n"/>
       <c r="L164" s="1" t="n"/>
       <c r="M164" s="1" t="inlineStr">
         <is>
-          <t>WBU</t>
+          <t>NBU</t>
         </is>
       </c>
       <c r="N164" s="1" t="n"/>
